--- a/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,0</t>
+          <t>-4,97; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,71</t>
+          <t>-1,45; 7,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,11</t>
+          <t>-3,14; 3,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,0</t>
+          <t>-5,45; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,09</t>
+          <t>-2,97; 0,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,42</t>
+          <t>-2,24; 2,4</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,77</t>
+          <t>-0,56; 0,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,18</t>
+          <t>-0,37; 1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,77</t>
+          <t>-0,47; 0,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,19</t>
+          <t>-0,87; 0,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,61</t>
+          <t>-0,35; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,57</t>
+          <t>-0,33; 0,53</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,94; 689,11</t>
+          <t>-71,27; 509,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,16; 616,45</t>
+          <t>-69,15; 514,9</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,59</t>
+          <t>-0,31; 2,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,88</t>
+          <t>-0,45; 2,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,0</t>
+          <t>-3,0; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,11</t>
+          <t>-2,15; 1,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,74</t>
+          <t>-0,94; 0,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,11</t>
+          <t>-0,8; 1,05</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,96; 722,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,67</t>
+          <t>-0,5; 0,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,22</t>
+          <t>-0,26; 1,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,41</t>
+          <t>-0,85; 0,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,16</t>
+          <t>-0,9; 0,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,39</t>
+          <t>-0,47; 0,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,48</t>
+          <t>-0,38; 0,51</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 372,18</t>
+          <t>-77,53; 524,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 698,16</t>
+          <t>-46,36; 667,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 199,86</t>
+          <t>-84,88; 179,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 96,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,76; 122,68</t>
+          <t>-65,7; 115,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 148,55</t>
+          <t>-52,26; 160,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,13</t>
+          <t>-1,76; 7,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,08</t>
+          <t>-3,88; 2,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,0</t>
+          <t>-5,17; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,75</t>
+          <t>-2,65; 0,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,4</t>
+          <t>-2,23; 2,38</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,78</t>
+          <t>-0,53; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,17</t>
+          <t>-0,35; 1,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,68</t>
+          <t>-0,48; 0,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,22</t>
+          <t>-0,8; 0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,57</t>
+          <t>-0,28; 0,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,53</t>
+          <t>-0,35; 0,54</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,11; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,27; 509,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 514,9</t>
+          <t>-77,47; 591,36</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,63</t>
+          <t>-0,43; 2,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,17</t>
+          <t>-0,53; 2,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,0</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,12</t>
+          <t>-1,81; 1,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,88</t>
+          <t>-1,09; 0,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,05</t>
+          <t>-0,84; 1,12</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,68</t>
+          <t>-0,55; 0,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,15</t>
+          <t>-0,22; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,41</t>
+          <t>-0,87; 0,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,16</t>
+          <t>-0,94; 0,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,36</t>
+          <t>-0,47; 0,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,51</t>
+          <t>-0,37; 0,52</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 524,61</t>
+          <t>-76,44; 451,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 667,12</t>
+          <t>-39,9; 705,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,88; 179,27</t>
+          <t>-84,37; 213,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,94</t>
+          <t>-100,0; 145,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 115,02</t>
+          <t>-65,19; 107,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 160,29</t>
+          <t>-55,72; 160,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1,23</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,0</t>
+          <t>-3,13; 3,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 7,02</t>
+          <t>-4,95; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,43</t>
+          <t>-5,02; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,0</t>
+          <t>-1,45; 7,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,76</t>
+          <t>-2,63; 1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,38</t>
+          <t>-2,27; 2,42</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-0,21%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>86,57%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,21%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,88</t>
+          <t>-0,45; 0,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,22</t>
+          <t>-0,87; 0,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,75</t>
+          <t>-0,66; 0,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,24</t>
+          <t>-0,38; 1,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,53</t>
+          <t>-0,32; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,54</t>
+          <t>-0,35; 0,57</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-58,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>36,02%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>114,26%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-58,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,11; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-64,94; 689,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,47; 591,36</t>
+          <t>-74,16; 616,45</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,86</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,42</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,71</t>
+          <t>-3,01; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,19</t>
+          <t>-2,15; 1,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,0</t>
+          <t>-0,3; 2,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,28</t>
+          <t>-0,31; 1,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,68</t>
+          <t>-0,95; 0,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,12</t>
+          <t>-0,75; 1,11</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,49%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>188,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>140,09%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-15,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-86,96; 722,1</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,69</t>
+          <t>-0,77; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,24</t>
+          <t>-0,89; 0,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,4</t>
+          <t>-0,57; 0,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,17</t>
+          <t>-0,27; 1,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,33</t>
+          <t>-0,46; 0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,52</t>
+          <t>-0,4; 0,48</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-23,06%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-53,94%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>87,18%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-23,06%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-53,94%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 451,27</t>
+          <t>-87,48; 199,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 705,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,37; 213,01</t>
+          <t>-77,98; 372,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,89</t>
+          <t>-46,07; 698,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 107,81</t>
+          <t>-64,76; 122,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,72; 160,58</t>
+          <t>-58,31; 148,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,279 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.003235006142657607</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.557797784974329</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.425751566105369</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.234273105078692</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.7500053273077821</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.2562388575521126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,13; 3,11</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,95; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,02; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-1,45; 7,71</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 1,09</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 2,42</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.134556553941755</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.94779675874968</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.019135561588897</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.44609475861895</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.630592544210062</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.267117431426141</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,21%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>86,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-50,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-17,19%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.105099753911321</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.706041911137167</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.094786824073888</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.416174879893578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-0.002076653448772825</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.8656999819753131</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.503264644835497</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.171940055548562</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 0,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 0,19</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 0,77</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 1,18</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 0,61</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 0,57</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-58,72%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>114,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1083538661361553</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1711048424935829</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1210293240752996</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.3839615745800543</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.114914726540621</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.1028195155318602</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-64,94; 689,11</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-74,16; 616,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.4465426287407543</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.8731671830739822</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.6573515194267396</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.3849049045303973</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.3206495233857317</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.3523779820923642</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7687192957656472</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1881669086765742</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7707632870493647</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.182960085947691</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.6129801913215155</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.5668956036772296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 1,11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,3; 2,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,31; 1,88</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 0,74</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 1,11</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.3718524466828745</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.587203360520388</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.3601719386114977</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.142633702413983</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3680939872125425</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3293506983372214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-15,49%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>188,28%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>140,09%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-24,55%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.649395800535951</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7415765561380128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-86,96; 722,1</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>6.891103015857424</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>6.1645025030329</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +880,293 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.8588888316337744</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.133057099347335</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5697341139398103</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.4239184259553438</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.1392951747572371</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.158752615802848</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 0,41</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 0,16</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 0,67</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,27; 1,22</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,46; 0,39</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.00902997596182</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.145449583600569</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.3042640111251703</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.305297733735571</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.9458193783872029</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.748567703232432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-23,06%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-53,94%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-10,87%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.110532313545229</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.590735238384423</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.877316260551615</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.7436222575163733</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.114125316340184</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-87,48; 199,86</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-77,98; 372,18</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-46,07; 698,16</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-64,76; 122,68</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-58,31; 148,55</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1549177197871282</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1.882795492009515</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1.400919625207508</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2454936717217338</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.2797854456681103</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-0.8695653864256984</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>7.221019981644124</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.1309722579979223</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.3063908643657392</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.02189147226023275</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.4122520624623131</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.0567340644924608</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.04283561621157692</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7667653342088671</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.888767184163018</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.5727006489881862</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.2708792820480023</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.4611769243650932</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.3991322636916511</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.4116971760128696</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.158505662369191</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.674105569340817</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.215463074889526</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.3868255723017998</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.4849579473040403</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.2305745772884309</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.5393962440296937</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.04629334774930868</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.8717791047158504</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1087183787472566</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.08208505399399331</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.8747940575609561</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="n">
+        <v>-0.7797986897688316</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.4607133004242491</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.6476342529433742</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.5830558561714174</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>1.998623634625131</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="n">
+        <v>3.721774763606664</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>6.981582041670335</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.226764937869541</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.485500464334181</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1174,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
